--- a/NECP Scenario/Results/Regional Results/EL61_Capacity.xlsx
+++ b/NECP Scenario/Results/Regional Results/EL61_Capacity.xlsx
@@ -507,25 +507,25 @@
         <v>1</v>
       </c>
       <c r="B2">
-        <v>1.176539815904244E-11</v>
+        <v>1.737116711224625E-11</v>
       </c>
       <c r="C2">
-        <v>6.160911158800132E-12</v>
+        <v>9.09636681321087E-12</v>
       </c>
       <c r="D2">
-        <v>9.052356880553564E-12</v>
+        <v>1.336547513940968E-11</v>
       </c>
       <c r="E2">
-        <v>1.330098827331579E-11</v>
+        <v>1.963841074343424E-11</v>
       </c>
       <c r="F2">
-        <v>1.954359268071265E-11</v>
+        <v>2.885536015014873E-11</v>
       </c>
       <c r="G2">
-        <v>2.87158909687047E-11</v>
+        <v>4.239790458091832E-11</v>
       </c>
       <c r="H2">
-        <v>1.740402764216938E-10</v>
+        <v>2.569640276465312E-10</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -533,25 +533,25 @@
         <v>2</v>
       </c>
       <c r="B3">
-        <v>4.748798164436807E-08</v>
+        <v>6.881587009645683E-08</v>
       </c>
       <c r="C3">
-        <v>5.930910298921345E-08</v>
+        <v>8.46390988111652E-08</v>
       </c>
       <c r="D3">
-        <v>1.270442138134557E-07</v>
+        <v>1.859143629151019E-07</v>
       </c>
       <c r="E3">
-        <v>3.706467080646894E-07</v>
+        <v>4.87810448679997E-07</v>
       </c>
       <c r="F3">
-        <v>0.1067809830136542</v>
+        <v>0.1006050389261387</v>
       </c>
       <c r="G3">
-        <v>0.2204671926168123</v>
+        <v>0.2868934929099073</v>
       </c>
       <c r="H3">
-        <v>0.3902836584417948</v>
+        <v>0.3989633275944545</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -562,22 +562,22 @@
         <v>0</v>
       </c>
       <c r="C4">
-        <v>8.584376024595496E-09</v>
+        <v>1.312854917275332E-08</v>
       </c>
       <c r="D4">
-        <v>2.606661470496034E-08</v>
+        <v>4.413514757366461E-08</v>
       </c>
       <c r="E4">
-        <v>0.0017185276273421</v>
+        <v>0.0019261788881814</v>
       </c>
       <c r="F4">
-        <v>0.0049510231906565</v>
+        <v>0.0052987369106691</v>
       </c>
       <c r="G4">
-        <v>0.0103427603975475</v>
+        <v>0.0103428419727832</v>
       </c>
       <c r="H4">
-        <v>0.0159399079938532</v>
+        <v>0.0164842840600565</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -692,22 +692,22 @@
         <v>0</v>
       </c>
       <c r="C9">
-        <v>3.745881499506337E-08</v>
+        <v>5.388642823978624E-08</v>
       </c>
       <c r="D9">
-        <v>3.746929114501577E-08</v>
+        <v>5.39035961504461E-08</v>
       </c>
       <c r="E9">
-        <v>3.747897182204505E-08</v>
+        <v>5.391855866907465E-08</v>
       </c>
       <c r="F9">
-        <v>3.748680804087321E-08</v>
+        <v>5.393041623129882E-08</v>
       </c>
       <c r="G9">
-        <v>3.750049158111159E-08</v>
+        <v>5.395127347809483E-08</v>
       </c>
       <c r="H9">
-        <v>1.283405997309797E-07</v>
+        <v>1.925433422423777E-07</v>
       </c>
     </row>
     <row r="10" spans="1:8">
@@ -793,25 +793,25 @@
         <v>12</v>
       </c>
       <c r="B13">
-        <v>2.046020288004455</v>
+        <v>2.046020288005349</v>
       </c>
       <c r="C13">
-        <v>2.046020288006182</v>
+        <v>2.04602028800789</v>
       </c>
       <c r="D13">
-        <v>2.046020288010657</v>
+        <v>2.046020288012024</v>
       </c>
       <c r="E13">
-        <v>2.046020288017131</v>
+        <v>2.046020288021287</v>
       </c>
       <c r="F13">
-        <v>2.046020288030894</v>
+        <v>2.046020288039023</v>
       </c>
       <c r="G13">
-        <v>2.046020288057683</v>
+        <v>2.046020288073941</v>
       </c>
       <c r="H13">
-        <v>2.046020288319301</v>
+        <v>2.046020288386408</v>
       </c>
     </row>
     <row r="14" spans="1:8">
@@ -923,25 +923,25 @@
         <v>17</v>
       </c>
       <c r="B18">
-        <v>4.135696111936085E-08</v>
+        <v>5.866749538050793E-08</v>
       </c>
       <c r="C18">
-        <v>4.137479153089992E-08</v>
+        <v>5.869340829791354E-08</v>
       </c>
       <c r="D18">
-        <v>8.130614032511588E-08</v>
+        <v>1.202573555400933E-07</v>
       </c>
       <c r="E18">
-        <v>4.418626936741104E-07</v>
+        <v>5.476760809968698E-07</v>
       </c>
       <c r="F18">
-        <v>2.685548764091614E-06</v>
+        <v>7.55385973871722E-06</v>
       </c>
       <c r="G18">
-        <v>2.685863043503295E-06</v>
+        <v>7.554347998372689E-06</v>
       </c>
       <c r="H18">
-        <v>3.14026768145946E-06</v>
+        <v>7.563896947923736E-06</v>
       </c>
     </row>
     <row r="19" spans="1:8">
@@ -952,22 +952,22 @@
         <v>0</v>
       </c>
       <c r="C19">
-        <v>0.0792002667915819</v>
+        <v>0.0792002666984213</v>
       </c>
       <c r="D19">
-        <v>0.0792002668088912</v>
+        <v>0.0792002667278156</v>
       </c>
       <c r="E19">
-        <v>0.0792002668659656</v>
+        <v>0.0792002668260552</v>
       </c>
       <c r="F19">
-        <v>0.0792002669221625</v>
+        <v>0.0792002668854072</v>
       </c>
       <c r="G19">
-        <v>0.07920026694695111</v>
+        <v>0.0792002669221389</v>
       </c>
       <c r="H19">
-        <v>0.07920026697521861</v>
+        <v>0.0792002669637985</v>
       </c>
     </row>
     <row r="20" spans="1:8">
@@ -1027,25 +1027,25 @@
         <v>21</v>
       </c>
       <c r="B22">
-        <v>3.072201070633903E-08</v>
+        <v>4.52490900446426E-08</v>
       </c>
       <c r="C22">
-        <v>3.073965408292208E-08</v>
+        <v>4.52751202899474E-08</v>
       </c>
       <c r="D22">
-        <v>3.086375468928309E-08</v>
+        <v>4.546247760344653E-08</v>
       </c>
       <c r="E22">
-        <v>4.136208647027701E-08</v>
+        <v>6.111752896360902E-08</v>
       </c>
       <c r="F22">
-        <v>5.796153348024774E-08</v>
+        <v>8.570497152014E-08</v>
       </c>
       <c r="G22">
-        <v>8.285281724809107E-08</v>
+        <v>1.227375915748278E-07</v>
       </c>
       <c r="H22">
-        <v>5.147029691127933E-07</v>
+        <v>7.638225893392905E-07</v>
       </c>
     </row>
     <row r="23" spans="1:8">
@@ -1082,22 +1082,22 @@
         <v>0</v>
       </c>
       <c r="C24">
-        <v>4.951588186174664E-09</v>
+        <v>7.194831396735879E-09</v>
       </c>
       <c r="D24">
-        <v>1.408528549953896E-08</v>
+        <v>2.056219749638449E-08</v>
       </c>
       <c r="E24">
-        <v>3.004218058057006E-08</v>
+        <v>4.431399729176437E-08</v>
       </c>
       <c r="F24">
-        <v>5.267605542733346E-08</v>
+        <v>7.861415304340799E-08</v>
       </c>
       <c r="G24">
-        <v>9.253004602434967E-08</v>
+        <v>1.384183192915682E-07</v>
       </c>
       <c r="H24">
-        <v>6.932649686611411E-07</v>
+        <v>1.325173388035454E-06</v>
       </c>
     </row>
     <row r="25" spans="1:8">
@@ -1160,22 +1160,22 @@
         <v>0</v>
       </c>
       <c r="C27">
-        <v>8.038503448721766E-09</v>
+        <v>1.15192656659929E-08</v>
       </c>
       <c r="D27">
-        <v>2.030927391947069E-08</v>
+        <v>2.920307745194037E-08</v>
       </c>
       <c r="E27">
-        <v>3.561590472545846E-08</v>
+        <v>5.051739637349268E-08</v>
       </c>
       <c r="F27">
-        <v>7.627408186137021E-08</v>
+        <v>1.031878822129068E-07</v>
       </c>
       <c r="G27">
-        <v>1.982624705165065E-07</v>
+        <v>2.686204778370539E-07</v>
       </c>
       <c r="H27">
-        <v>4.127624670970704E-05</v>
+        <v>5.465986793012579E-06</v>
       </c>
     </row>
     <row r="28" spans="1:8">
@@ -1212,22 +1212,22 @@
         <v>0</v>
       </c>
       <c r="C29">
-        <v>1.001398735063567E-08</v>
+        <v>1.466216151298196E-08</v>
       </c>
       <c r="D29">
-        <v>3.412934441740046E-08</v>
+        <v>5.225104186142206E-08</v>
       </c>
       <c r="E29">
-        <v>1.367106669834233E-07</v>
+        <v>2.691758717831673E-07</v>
       </c>
       <c r="F29">
-        <v>0.1072768682360449</v>
+        <v>0.337350865845967</v>
       </c>
       <c r="G29">
-        <v>0.3373508701198466</v>
+        <v>0.3373508700573328</v>
       </c>
       <c r="H29">
-        <v>0.337350870663561</v>
+        <v>0.3373508706389432</v>
       </c>
     </row>
     <row r="30" spans="1:8">
@@ -1264,22 +1264,22 @@
         <v>0</v>
       </c>
       <c r="C31">
-        <v>5.959685138334207E-09</v>
+        <v>8.642238066056877E-09</v>
       </c>
       <c r="D31">
-        <v>7.362459949748339E-09</v>
+        <v>1.084878035040984E-08</v>
       </c>
       <c r="E31">
-        <v>1.183796974871569E-08</v>
+        <v>1.752424894892941E-08</v>
       </c>
       <c r="F31">
-        <v>1.743064338747412E-08</v>
+        <v>2.57859916859872E-08</v>
       </c>
       <c r="G31">
-        <v>2.495105480595406E-08</v>
+        <v>3.714280311218913E-08</v>
       </c>
       <c r="H31">
-        <v>1.536641247653316E-07</v>
+        <v>2.368780158898966E-07</v>
       </c>
     </row>
     <row r="32" spans="1:8">
@@ -1316,22 +1316,22 @@
         <v>0</v>
       </c>
       <c r="C33">
-        <v>2.13094425269496E-08</v>
+        <v>2.964450527925941E-08</v>
       </c>
       <c r="D33">
-        <v>2.549751363099513E-08</v>
+        <v>3.696281487397466E-08</v>
       </c>
       <c r="E33">
-        <v>4.751469097486132E-08</v>
+        <v>6.995941090051883E-08</v>
       </c>
       <c r="F33">
-        <v>6.200138665416954E-08</v>
+        <v>9.23866840988146E-08</v>
       </c>
       <c r="G33">
-        <v>7.707041694045426E-08</v>
+        <v>1.146266940267847E-07</v>
       </c>
       <c r="H33">
-        <v>4.270365307547675E-07</v>
+        <v>7.01803203764182E-07</v>
       </c>
     </row>
     <row r="34" spans="1:8">
